--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F549C55-2923-4FB9-9A8D-349B792D06F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAF0765-328A-4C20-8D73-1E4443D9341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="91">
   <si>
     <t>Result</t>
   </si>
@@ -249,42 +249,6 @@
     <t>N</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 03:54:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 03:55:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 03:56:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 03:57:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 03:57:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 03:58:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 03:59:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 04:00:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 04:01:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 04:02:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 04:03:27 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Jun 18 22:47:32 IST 2026</t>
   </si>
   <si>
@@ -294,9 +258,6 @@
     <t>Thu Jun 18 22:49:23 IST 2026</t>
   </si>
   <si>
-    <t>Thu Jun 18 22:51:44 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Jun 18 22:53:25 IST 2026</t>
   </si>
   <si>
@@ -312,71 +273,49 @@
     <t>Thu Jun 18 22:56:21 IST 2026</t>
   </si>
   <si>
-    <t>Thu Jun 18 23:05:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:49:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:50:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:51:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:51:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:52:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:53:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:54:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:55:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:55:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:56:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 16:57:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:08:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:10:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:11:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:13:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:15:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:16:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:18:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:20:00 IST 2026</t>
+    <t>Tue Oct 13 01:23:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:24:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:24:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:25:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:25:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:26:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:27:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:28:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:28:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:29:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:30:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:49:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:50:36 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -901,25 +840,25 @@
   <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="21" width="15.36328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="5.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
-    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
-    <col min="14" max="15" customWidth="true" style="6" width="14.453125" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
-    <col min="20" max="28" style="6" width="8.7265625" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.36328125" style="21" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="5.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="11.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="15" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="15" width="14.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="20" max="28" width="8.7265625" style="6" collapsed="1"/>
+    <col min="29" max="16384" width="8.7265625" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.25">
@@ -1009,11 +948,11 @@
       </c>
     </row>
     <row r="2" spans="1:28" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B2" t="s" s="21">
-        <v>92</v>
+      <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>78</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -1055,11 +994,11 @@
       <c r="AB2" s="9"/>
     </row>
     <row r="3" spans="1:28" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s" s="21">
-        <v>93</v>
+      <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -1082,11 +1021,11 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="25" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s" s="21">
-        <v>94</v>
+      <c r="A4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1111,11 +1050,11 @@
       </c>
     </row>
     <row r="5" spans="1:28" ht="38" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B5" t="s" s="21">
-        <v>95</v>
+      <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1164,11 +1103,11 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B6" t="s" s="21">
-        <v>96</v>
+      <c r="A6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1217,11 +1156,11 @@
       </c>
     </row>
     <row r="7" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B7" t="s" s="21">
-        <v>97</v>
+      <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1273,11 +1212,11 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s" s="21">
-        <v>98</v>
+      <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -1305,11 +1244,11 @@
       </c>
     </row>
     <row r="9" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s" s="21">
-        <v>99</v>
+      <c r="A9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1334,11 +1273,11 @@
       </c>
     </row>
     <row r="10" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B10" t="s" s="21">
-        <v>100</v>
+      <c r="A10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>86</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1363,11 +1302,11 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B11" t="s" s="21">
-        <v>101</v>
+      <c r="A11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>87</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>67</v>
@@ -1422,11 +1361,11 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B12" t="s" s="21">
-        <v>102</v>
+      <c r="A12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>88</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
@@ -1501,32 +1440,32 @@
   <dimension ref="A1:AC11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="11" width="36.0" collapsed="true"/>
-    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="6" width="13.453125" collapsed="true"/>
-    <col min="16" max="17" style="6" width="8.7265625" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="19" max="22" style="6" width="8.7265625" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
-    <col min="25" max="25" customWidth="true" style="6" width="6.0" collapsed="true"/>
-    <col min="26" max="26" customWidth="true" style="6" width="5.90625" collapsed="true"/>
-    <col min="27" max="27" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="28" max="28" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
-    <col min="29" max="29" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
-    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="36" style="11" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="13.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="17" width="8.7265625" style="6" collapsed="1"/>
+    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="22" width="8.7265625" style="6" collapsed="1"/>
+    <col min="23" max="23" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="6" style="6" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="5.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
+    <col min="30" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -1619,11 +1558,11 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B2" t="s" s="6">
-        <v>82</v>
+      <c r="A2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
@@ -1666,11 +1605,11 @@
       </c>
     </row>
     <row r="3" spans="1:29" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s" s="6">
-        <v>83</v>
+      <c r="A3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
@@ -1681,11 +1620,11 @@
       </c>
     </row>
     <row r="4" spans="1:29" ht="13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s" s="6">
-        <v>84</v>
+      <c r="A4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>30</v>
@@ -1698,11 +1637,11 @@
       </c>
     </row>
     <row r="5" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="6">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s" s="6">
-        <v>109</v>
+      <c r="A5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1746,11 +1685,11 @@
       </c>
     </row>
     <row r="6" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="6">
-        <v>70</v>
-      </c>
-      <c r="B6" t="s" s="6">
-        <v>110</v>
+      <c r="A6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1776,11 +1715,11 @@
       </c>
     </row>
     <row r="7" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B7" t="s" s="6">
-        <v>86</v>
+      <c r="A7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
@@ -1805,11 +1744,11 @@
       </c>
     </row>
     <row r="8" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s" s="6">
-        <v>87</v>
+      <c r="A8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
@@ -1834,11 +1773,11 @@
       </c>
     </row>
     <row r="9" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s" s="6">
-        <v>88</v>
+      <c r="A9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
@@ -1857,11 +1796,11 @@
       </c>
     </row>
     <row r="10" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B10" t="s" s="6">
-        <v>89</v>
+      <c r="A10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
@@ -1907,11 +1846,11 @@
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="B11" t="s" s="6">
-        <v>90</v>
+      <c r="A11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>
